--- a/ScrapingManga/Estrazione_OnePiece.xlsx
+++ b/ScrapingManga/Estrazione_OnePiece.xlsx
@@ -425,258 +425,918 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Titolo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Prezzo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>One piece. New edition. Vol. 1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>5,60 €</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>One piece. New edition. Vol. 2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>4,94 €</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>One piece. New edition. Vol. 3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>5,60 €</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LEGO One Piece (75639). La nave pirata Going Merry</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>129,99 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 16</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 18</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 22</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 21</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>One piece. Vol. 112</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>One piece. New edition. Vol. 27</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4,94 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 28</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 31</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 35</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 33</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>One piece. New edition. Vol. 30</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4,94 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 34</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>One piece. New edition. Vol. 37</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4,94 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 34</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4,94 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 35</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>5,60 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LEGO One Piece (75639). La nave pirata Going Merry</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>123,49 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LEGO One Piece (75636). La capanna del villaggio Foosha</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>28,49 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 40</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>One piece. New edition. Vol. 32</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>5,60 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 29</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4,94 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 28</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>4,94 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FUNKO POP Animation: One Piece (Refresh)- Sanji</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>16,14 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 5</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>4,94 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 7</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5,60 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5,60 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 26</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>4,94 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 4</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>5,60 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 40</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5,60 €</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>One piece. New edition. Vol. 6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>4,94 €</t>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 49</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 36</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 39</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 42</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 43</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 48</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>One piece. Celebration edition. Ediz. speciale. Vol. 99</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6,56 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 59</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 50</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 58</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 57</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 44</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 46</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 45</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 41</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 47</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 56</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>One piece. Vol. 110</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 38</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 77</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>5,60 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 78</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>One piece. New edition. Vol. 82</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4,94 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>One piece. Le ricette piratesche di Sanji</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>18,90 €</t>
         </is>
       </c>
     </row>
